--- a/artfynd/A 22024-2024 artfynd.xlsx
+++ b/artfynd/A 22024-2024 artfynd.xlsx
@@ -916,10 +916,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117968519</v>
+        <v>117968570</v>
       </c>
       <c r="B4" t="n">
-        <v>90499</v>
+        <v>8405</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,34 +928,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -963,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525034</v>
+        <v>525085</v>
       </c>
       <c r="R4" t="n">
-        <v>6547631</v>
+        <v>6547682</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1026,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117968570</v>
+        <v>117968519</v>
       </c>
       <c r="B5" t="n">
-        <v>8405</v>
+        <v>90499</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,36 +1040,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525085</v>
+        <v>525034</v>
       </c>
       <c r="R5" t="n">
-        <v>6547682</v>
+        <v>6547631</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 22024-2024 artfynd.xlsx
+++ b/artfynd/A 22024-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117968591</v>
+        <v>117968570</v>
       </c>
       <c r="B3" t="n">
         <v>8405</v>
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525108</v>
+        <v>525085</v>
       </c>
       <c r="R3" t="n">
-        <v>6547668</v>
+        <v>6547682</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -916,7 +916,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117968570</v>
+        <v>117968591</v>
       </c>
       <c r="B4" t="n">
         <v>8405</v>
@@ -965,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525085</v>
+        <v>525108</v>
       </c>
       <c r="R4" t="n">
-        <v>6547682</v>
+        <v>6547668</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117968519</v>
+        <v>117968612</v>
       </c>
       <c r="B5" t="n">
-        <v>90499</v>
+        <v>57716</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,30 +1044,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1075,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525034</v>
+        <v>525138</v>
       </c>
       <c r="R5" t="n">
-        <v>6547631</v>
+        <v>6547667</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1119,7 +1124,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1138,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117968612</v>
+        <v>117968519</v>
       </c>
       <c r="B6" t="n">
-        <v>57715</v>
+        <v>90501</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,35 +1158,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103001</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1190,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525138</v>
+        <v>525034</v>
       </c>
       <c r="R6" t="n">
-        <v>6547667</v>
+        <v>6547631</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1234,6 +1233,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22024-2024 artfynd.xlsx
+++ b/artfynd/A 22024-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>78944975</v>
+        <v>117968519</v>
       </c>
       <c r="B2" t="n">
-        <v>106757</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,53 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220228</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bännebo kanal vid vägen, Nrk</t>
+          <t>Varbergstorp, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>524740.7299295224</v>
+        <v>525034</v>
       </c>
       <c r="R2" t="n">
-        <v>6547631.394851997</v>
+        <v>6547631</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,22 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-06-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-06-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,58 +768,56 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Arne Holmer</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Arne Holmer</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117968591</v>
+        <v>117968612</v>
       </c>
       <c r="B3" t="n">
-        <v>8405</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>103001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -853,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525108</v>
+        <v>525138</v>
       </c>
       <c r="R3" t="n">
-        <v>6547668</v>
+        <v>6547667</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -897,7 +871,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -919,12 +892,7 @@
         <v>117968570</v>
       </c>
       <c r="B4" t="n">
-        <v>8405</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,49 +996,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117968612</v>
+        <v>117968591</v>
       </c>
       <c r="B5" t="n">
-        <v>57718</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103001</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1080,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525138</v>
+        <v>525108</v>
       </c>
       <c r="R5" t="n">
-        <v>6547667</v>
+        <v>6547668</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1124,6 +1084,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1142,57 +1103,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117968519</v>
+        <v>117968458</v>
       </c>
       <c r="B6" t="n">
-        <v>90504</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>219875</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Varbergstorp, Nrk</t>
+          <t>Mörket, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525034</v>
+        <v>524715</v>
       </c>
       <c r="R6" t="n">
-        <v>6547631</v>
+        <v>6547620</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1249,6 +1206,220 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>78944975</v>
+      </c>
+      <c r="B7" t="n">
+        <v>109866</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220228</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sommarfibbla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Leontodon hispidus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bännebo kanal vid vägen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>524741</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6547631</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2015-06-22</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2015-06-22</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Arne Holmer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Arne Holmer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>54040408</v>
+      </c>
+      <c r="B8" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bännebo kanal vid vägen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>524741</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6547632</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sköllersta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2015-06-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2015-06-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Arne Holmer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Arne Holmer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22024-2024 artfynd.xlsx
+++ b/artfynd/A 22024-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117968519</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117968612</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117968570</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117968591</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117968458</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78944975</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1420,8 +1455,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54040408</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>